--- a/Result/profitability/3526.xlsx
+++ b/Result/profitability/3526.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8975</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>47.42250000000001</v>
+        <v>46.70125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>3.44625</v>
+        <v>3.34125</v>
       </c>
       <c r="N3" t="n">
-        <v>43.66125</v>
+        <v>43.1675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.83</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1475</v>
+        <v>3.1825</v>
       </c>
       <c r="N4" t="n">
-        <v>41.345</v>
+        <v>40.78625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.78</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8575</v>
+        <v>2.8875</v>
       </c>
       <c r="N5" t="n">
-        <v>38.91625000000001</v>
+        <v>38.35875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.65</v>
       </c>
       <c r="M6" t="n">
-        <v>2.54625</v>
+        <v>2.58125</v>
       </c>
       <c r="N6" t="n">
-        <v>36.86875000000001</v>
+        <v>36.835</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.49</v>
       </c>
       <c r="M7" t="n">
-        <v>2.345</v>
+        <v>2.31</v>
       </c>
       <c r="N7" t="n">
-        <v>36.37125</v>
+        <v>36.31</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.86</v>
       </c>
       <c r="M8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="N8" t="n">
-        <v>35.70875</v>
+        <v>35.36125000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>2.135</v>
       </c>
       <c r="N10" t="n">
-        <v>36.77375</v>
+        <v>36.77375000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D75" t="n">
+        <v>634</v>
+      </c>
+      <c r="E75" t="n">
+        <v>576</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="G75" t="n">
+        <v>357</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>29.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>349</v>
+      </c>
+      <c r="K75" t="n">
+        <v>290</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4.4575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>50.37375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.3200000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.06808510638297882</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.780000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05518062723302897</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2400000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.05797101449275366</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.460000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08567038033038799</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
